--- a/data/trans_orig/IP74A1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP74A1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto la hipoteca en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de la hipoteca en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
